--- a/salidas/empresas/WMT.xlsx
+++ b/salidas/empresas/WMT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>10.18526744842529</v>
+        <v>10.18526458740234</v>
       </c>
       <c r="C2" t="n">
         <v>15.36999988555908</v>
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>10.47351169586182</v>
+        <v>10.47351551055908</v>
       </c>
       <c r="C4" t="n">
         <v>15.74666690826416</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>9.983535766601562</v>
+        <v>9.983537673950195</v>
       </c>
       <c r="C5" t="n">
         <v>15.01000022888184</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>10.77945423126221</v>
+        <v>10.77945232391357</v>
       </c>
       <c r="C6" t="n">
         <v>16.14999961853027</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>10.71715450286865</v>
+        <v>10.71715927124023</v>
       </c>
       <c r="C7" t="n">
         <v>16.05666732788086</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>9.900633811950684</v>
+        <v>9.900634765625</v>
       </c>
       <c r="C8" t="n">
         <v>14.83333301544189</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>9.98724365234375</v>
+        <v>9.987241744995117</v>
       </c>
       <c r="C9" t="n">
         <v>14.90666675567627</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>11.01455307006836</v>
+        <v>11.01455211639404</v>
       </c>
       <c r="C10" t="n">
         <v>16.44000053405762</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>11.00561714172363</v>
+        <v>11.00561428070068</v>
       </c>
       <c r="C11" t="n">
         <v>16.42666625976562</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>10.29543495178223</v>
+        <v>10.29543304443359</v>
       </c>
       <c r="C12" t="n">
         <v>15.36666679382324</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>10.35140037536621</v>
+        <v>10.35139942169189</v>
       </c>
       <c r="C13" t="n">
         <v>15.39333343505859</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>10.68986511230469</v>
+        <v>10.68986701965332</v>
       </c>
       <c r="C14" t="n">
         <v>15.89666652679443</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>10.82884311676025</v>
+        <v>10.8288402557373</v>
       </c>
       <c r="C15" t="n">
         <v>16.10333251953125</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>10.57437133789062</v>
+        <v>10.57437038421631</v>
       </c>
       <c r="C16" t="n">
         <v>15.64999961853027</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>10.79283714294434</v>
+        <v>10.79283905029297</v>
       </c>
       <c r="C17" t="n">
         <v>15.97333335876465</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>10.77052593231201</v>
+        <v>10.77052783966064</v>
       </c>
       <c r="C18" t="n">
         <v>15.86666679382324</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>10.88592720031738</v>
+        <v>10.88592529296875</v>
       </c>
       <c r="C19" t="n">
         <v>16.03666687011719</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>10.39717483520508</v>
+        <v>10.39717960357666</v>
       </c>
       <c r="C20" t="n">
         <v>15.31666660308838</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>9.922042846679688</v>
+        <v>9.922039985656738</v>
       </c>
       <c r="C21" t="n">
         <v>14.54333305358887</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>9.926594734191895</v>
+        <v>9.926590919494629</v>
       </c>
       <c r="C22" t="n">
         <v>14.55000019073486</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>10.28135204315186</v>
+        <v>10.28135299682617</v>
       </c>
       <c r="C23" t="n">
         <v>15.06999969482422</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>10.89309597015381</v>
+        <v>10.89309978485107</v>
       </c>
       <c r="C24" t="n">
         <v>15.96666717529297</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>10.85766792297363</v>
+        <v>10.85767269134521</v>
       </c>
       <c r="C25" t="n">
         <v>15.84333324432373</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>11.59096145629883</v>
+        <v>11.59096050262451</v>
       </c>
       <c r="C26" t="n">
         <v>16.91333389282227</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>11.32825374603271</v>
+        <v>11.32825469970703</v>
       </c>
       <c r="C27" t="n">
         <v>16.53000068664551</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>12.09139728546143</v>
+        <v>12.09140014648438</v>
       </c>
       <c r="C28" t="n">
         <v>17.55999946594238</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>13.30788326263428</v>
+        <v>13.30788230895996</v>
       </c>
       <c r="C29" t="n">
         <v>19.32666778564453</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>13.30871391296387</v>
+        <v>13.30871200561523</v>
       </c>
       <c r="C30" t="n">
         <v>19.24666786193848</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>12.9537467956543</v>
+        <v>12.9537525177002</v>
       </c>
       <c r="C31" t="n">
         <v>18.73333358764648</v>
@@ -1052,7 +1064,7 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>13.67018127441406</v>
+        <v>13.67017459869385</v>
       </c>
       <c r="C33" t="n">
         <v>19.69000053405762</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>13.85994720458984</v>
+        <v>13.85994434356689</v>
       </c>
       <c r="C34" t="n">
         <v>19.96333312988281</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>12.91573905944824</v>
+        <v>12.91573810577393</v>
       </c>
       <c r="C35" t="n">
         <v>18.60333251953125</v>
@@ -1128,7 +1140,7 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>13.02971935272217</v>
+        <v>13.02972030639648</v>
       </c>
       <c r="C37" t="n">
         <v>18.68666648864746</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>10.95184326171875</v>
+        <v>10.95184516906738</v>
       </c>
       <c r="C38" t="n">
         <v>15.70666694641113</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>11.44458293914795</v>
+        <v>11.44458198547363</v>
       </c>
       <c r="C39" t="n">
         <v>16.41333389282227</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>12.17762565612793</v>
+        <v>12.17762660980225</v>
       </c>
       <c r="C40" t="n">
         <v>17.36666679382324</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>11.78027439117432</v>
+        <v>11.78027820587158</v>
       </c>
       <c r="C41" t="n">
         <v>16.79999923706055</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>11.68870449066162</v>
+        <v>11.6887035369873</v>
       </c>
       <c r="C42" t="n">
         <v>16.57999992370605</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>11.38320827484131</v>
+        <v>11.38320922851562</v>
       </c>
       <c r="C43" t="n">
         <v>16.14666748046875</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>11.72160148620605</v>
+        <v>11.72160243988037</v>
       </c>
       <c r="C44" t="n">
         <v>16.62666702270508</v>
@@ -1299,7 +1311,7 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>11.59923648834229</v>
+        <v>11.59923362731934</v>
       </c>
       <c r="C46" t="n">
         <v>16.36333274841309</v>
@@ -1343,11 +1355,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>11.73864650726318</v>
+        <v>11.73864269256592</v>
       </c>
       <c r="C47" t="n">
         <v>16.55999946594238</v>
@@ -1368,11 +1380,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>12.88935279846191</v>
+        <v>12.88934898376465</v>
       </c>
       <c r="C48" t="n">
         <v>18.1833324432373</v>
@@ -1393,11 +1405,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>12.6931266784668</v>
+        <v>12.69312763214111</v>
       </c>
       <c r="C49" t="n">
         <v>17.8166675567627</v>
@@ -1418,11 +1430,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>12.68837547302246</v>
+        <v>12.68838024139404</v>
       </c>
       <c r="C50" t="n">
         <v>17.80999946594238</v>
@@ -1443,11 +1455,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>12.84035873413086</v>
+        <v>12.84036159515381</v>
       </c>
       <c r="C51" t="n">
         <v>18.0233325958252</v>
@@ -1468,11 +1480,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>13.27812385559082</v>
+        <v>13.27811813354492</v>
       </c>
       <c r="C52" t="n">
         <v>18.53333282470703</v>
@@ -1493,7 +1505,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
@@ -1518,11 +1530,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>12.14464282989502</v>
+        <v>12.14464378356934</v>
       </c>
       <c r="C54" t="n">
         <v>16.85333251953125</v>
@@ -1543,11 +1555,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>11.54653644561768</v>
+        <v>11.54653453826904</v>
       </c>
       <c r="C55" t="n">
         <v>16.0233325958252</v>
@@ -1568,11 +1580,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>12.29596614837646</v>
+        <v>12.29597091674805</v>
       </c>
       <c r="C56" t="n">
         <v>17.06333351135254</v>
@@ -1593,11 +1605,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>12.11404228210449</v>
+        <v>12.11404800415039</v>
       </c>
       <c r="C57" t="n">
         <v>16.71333312988281</v>
@@ -1618,11 +1630,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>12.93067169189453</v>
+        <v>12.93066596984863</v>
       </c>
       <c r="C58" t="n">
         <v>17.84000015258789</v>
@@ -1643,11 +1655,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>13.08771419525146</v>
+        <v>13.08771514892578</v>
       </c>
       <c r="C59" t="n">
         <v>18.05666732788086</v>
@@ -1668,11 +1680,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>13.06838321685791</v>
+        <v>13.06838798522949</v>
       </c>
       <c r="C60" t="n">
         <v>18.03000068664551</v>
@@ -1693,11 +1705,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>13.10178375244141</v>
+        <v>13.1017894744873</v>
       </c>
       <c r="C61" t="n">
         <v>17.9766674041748</v>
@@ -1718,11 +1730,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>13.62167644500732</v>
+        <v>13.62168121337891</v>
       </c>
       <c r="C62" t="n">
         <v>18.69000053405762</v>
@@ -1743,11 +1755,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>12.6280517578125</v>
+        <v>12.62805461883545</v>
       </c>
       <c r="C63" t="n">
         <v>17.32666778564453</v>
@@ -1768,11 +1780,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>12.73369216918945</v>
+        <v>12.7336893081665</v>
       </c>
       <c r="C64" t="n">
         <v>17.35000038146973</v>
@@ -1797,11 +1809,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>13.45049476623535</v>
+        <v>13.45049571990967</v>
       </c>
       <c r="C65" t="n">
         <v>18.32666778564453</v>
@@ -1826,11 +1838,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>13.59859466552734</v>
+        <v>13.59859275817871</v>
       </c>
       <c r="C66" t="n">
         <v>18.40666770935059</v>
@@ -1855,11 +1867,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>13.08636569976807</v>
+        <v>13.08636856079102</v>
       </c>
       <c r="C67" t="n">
         <v>17.71333312988281</v>
@@ -1884,11 +1896,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>12.98047161102295</v>
+        <v>12.98047924041748</v>
       </c>
       <c r="C68" t="n">
         <v>17.56999969482422</v>
@@ -1913,7 +1925,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
@@ -1942,11 +1954,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>12.87346363067627</v>
+        <v>12.87346172332764</v>
       </c>
       <c r="C70" t="n">
         <v>17.29999923706055</v>
@@ -1971,11 +1983,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>14.06903743743896</v>
+        <v>14.06903839111328</v>
       </c>
       <c r="C71" t="n">
         <v>18.90666770935059</v>
@@ -2000,11 +2012,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>14.60977172851562</v>
+        <v>14.60976219177246</v>
       </c>
       <c r="C72" t="n">
         <v>19.63333320617676</v>
@@ -2029,11 +2041,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>14.91570663452148</v>
+        <v>14.91570377349854</v>
       </c>
       <c r="C73" t="n">
         <v>19.92000007629395</v>
@@ -2058,11 +2070,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>15.31505298614502</v>
+        <v>15.31505584716797</v>
       </c>
       <c r="C74" t="n">
         <v>20.45333290100098</v>
@@ -2087,11 +2099,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>14.74597835540771</v>
+        <v>14.74598121643066</v>
       </c>
       <c r="C75" t="n">
         <v>19.69333267211914</v>
@@ -2116,11 +2128,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>15.37736034393311</v>
+        <v>15.377366065979</v>
       </c>
       <c r="C76" t="n">
         <v>20.39999961853027</v>
@@ -2145,7 +2157,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
@@ -2174,11 +2186,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>16.65042495727539</v>
+        <v>16.65043640136719</v>
       </c>
       <c r="C78" t="n">
         <v>21.94000053405762</v>
@@ -2203,11 +2215,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>17.63700866699219</v>
+        <v>17.63701057434082</v>
       </c>
       <c r="C79" t="n">
         <v>23.23999977111816</v>
@@ -2232,11 +2244,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>18.82849311828613</v>
+        <v>18.8284912109375</v>
       </c>
       <c r="C80" t="n">
         <v>24.80999946594238</v>
@@ -2261,7 +2273,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
@@ -2290,11 +2302,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>18.77008438110352</v>
+        <v>18.77009010314941</v>
       </c>
       <c r="C82" t="n">
         <v>24.60000038146973</v>
@@ -2319,11 +2331,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>19.08037948608398</v>
+        <v>19.08037567138672</v>
       </c>
       <c r="C83" t="n">
         <v>25.00666618347168</v>
@@ -2348,11 +2360,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>18.31736755371094</v>
+        <v>18.3173656463623</v>
       </c>
       <c r="C84" t="n">
         <v>24.00666618347168</v>
@@ -2377,11 +2389,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>17.4497241973877</v>
+        <v>17.44972801208496</v>
       </c>
       <c r="C85" t="n">
         <v>22.74333381652832</v>
@@ -2406,11 +2418,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>17.88961982727051</v>
+        <v>17.88962364196777</v>
       </c>
       <c r="C86" t="n">
         <v>23.3166675567627</v>
@@ -2435,11 +2447,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>18.10188865661621</v>
+        <v>18.10188293457031</v>
       </c>
       <c r="C87" t="n">
         <v>23.59333229064941</v>
@@ -2464,11 +2476,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>19.26113700866699</v>
+        <v>19.26113891601562</v>
       </c>
       <c r="C88" t="n">
         <v>24.94333267211914</v>
@@ -2493,11 +2505,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>20.00502967834473</v>
+        <v>20.00502395629883</v>
       </c>
       <c r="C89" t="n">
         <v>25.90666770935059</v>
@@ -2522,11 +2534,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>19.37925910949707</v>
+        <v>19.3792552947998</v>
       </c>
       <c r="C90" t="n">
         <v>24.9466667175293</v>
@@ -2551,11 +2563,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>19.28862190246582</v>
+        <v>19.28862571716309</v>
       </c>
       <c r="C91" t="n">
         <v>24.82999992370605</v>
@@ -2580,11 +2592,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>20.18197631835938</v>
+        <v>20.18198204040527</v>
       </c>
       <c r="C92" t="n">
         <v>25.97999954223633</v>
@@ -2609,11 +2621,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>19.01237869262695</v>
+        <v>19.01237297058105</v>
       </c>
       <c r="C93" t="n">
         <v>24.32666778564453</v>
@@ -2638,11 +2650,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>19.26767539978027</v>
+        <v>19.26767730712891</v>
       </c>
       <c r="C94" t="n">
         <v>24.65333366394043</v>
@@ -2667,11 +2679,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>19.9945125579834</v>
+        <v>19.99452018737793</v>
       </c>
       <c r="C95" t="n">
         <v>25.58333206176758</v>
@@ -2696,11 +2708,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>21.10431098937988</v>
+        <v>21.10431289672852</v>
       </c>
       <c r="C96" t="n">
         <v>27.00333213806152</v>
@@ -2725,11 +2737,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>20.61924743652344</v>
+        <v>20.61924362182617</v>
       </c>
       <c r="C97" t="n">
         <v>26.22999954223633</v>
@@ -2754,11 +2766,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>19.5684986114502</v>
+        <v>19.56850242614746</v>
       </c>
       <c r="C98" t="n">
         <v>24.89333343505859</v>
@@ -2783,11 +2795,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>19.57374572753906</v>
+        <v>19.57374382019043</v>
       </c>
       <c r="C99" t="n">
         <v>24.89999961853027</v>
@@ -2812,7 +2824,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -2841,11 +2853,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>21.02127265930176</v>
+        <v>21.02126502990723</v>
       </c>
       <c r="C101" t="n">
         <v>26.56999969482422</v>
@@ -2870,7 +2882,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
@@ -2899,11 +2911,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>19.92016983032227</v>
+        <v>19.92017364501953</v>
       </c>
       <c r="C103" t="n">
         <v>25.0233325958252</v>
@@ -2928,11 +2940,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>19.52479934692383</v>
+        <v>19.52478981018066</v>
       </c>
       <c r="C104" t="n">
         <v>24.52666664123535</v>
@@ -2957,11 +2969,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>20.1662540435791</v>
+        <v>20.166259765625</v>
       </c>
       <c r="C105" t="n">
         <v>25.16666793823242</v>
@@ -2986,11 +2998,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>20.42535400390625</v>
+        <v>20.42535591125488</v>
       </c>
       <c r="C106" t="n">
         <v>25.48999977111816</v>
@@ -3015,7 +3027,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
@@ -3044,11 +3056,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>23.38217735290527</v>
+        <v>23.38217926025391</v>
       </c>
       <c r="C108" t="n">
         <v>29.18000030517578</v>
@@ -3073,11 +3085,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>23.06694221496582</v>
+        <v>23.06693649291992</v>
       </c>
       <c r="C109" t="n">
         <v>28.62666702270508</v>
@@ -3102,11 +3114,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>22.82519912719727</v>
+        <v>22.82520294189453</v>
       </c>
       <c r="C110" t="n">
         <v>28.32666778564453</v>
@@ -3131,11 +3143,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>22.54318046569824</v>
+        <v>22.54317283630371</v>
       </c>
       <c r="C111" t="n">
         <v>27.9766674041748</v>
@@ -3160,11 +3172,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>22.22463035583496</v>
+        <v>22.22462844848633</v>
       </c>
       <c r="C112" t="n">
         <v>27.41666793823242</v>
@@ -3189,11 +3201,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>21.08975219726562</v>
+        <v>21.08976364135742</v>
       </c>
       <c r="C113" t="n">
         <v>26.01666641235352</v>
@@ -3218,7 +3230,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
@@ -3247,11 +3259,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>19.28683662414551</v>
+        <v>19.28682708740234</v>
       </c>
       <c r="C115" t="n">
         <v>23.64333343505859</v>
@@ -3276,11 +3288,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>19.57234382629395</v>
+        <v>19.57234001159668</v>
       </c>
       <c r="C116" t="n">
         <v>23.99333381652832</v>
@@ -3305,7 +3317,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
@@ -3334,11 +3346,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>17.75126838684082</v>
+        <v>17.75126075744629</v>
       </c>
       <c r="C118" t="n">
         <v>21.61333274841309</v>
@@ -3363,11 +3375,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>15.67060947418213</v>
+        <v>15.67061424255371</v>
       </c>
       <c r="C119" t="n">
         <v>19.07999992370605</v>
@@ -3392,11 +3404,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>16.1086483001709</v>
+        <v>16.10863876342773</v>
       </c>
       <c r="C120" t="n">
         <v>19.61333274841309</v>
@@ -3421,11 +3433,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>16.92268371582031</v>
+        <v>16.92268943786621</v>
       </c>
       <c r="C121" t="n">
         <v>20.4333324432373</v>
@@ -3450,11 +3462,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>18.31957054138184</v>
+        <v>18.31956672668457</v>
       </c>
       <c r="C122" t="n">
         <v>22.1200008392334</v>
@@ -3479,11 +3491,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>18.31405067443848</v>
+        <v>18.31404685974121</v>
       </c>
       <c r="C123" t="n">
         <v>22.11333274841309</v>
@@ -3508,11 +3520,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>19.04755783081055</v>
+        <v>19.04755973815918</v>
       </c>
       <c r="C124" t="n">
         <v>22.82999992370605</v>
@@ -3537,11 +3549,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>18.59703254699707</v>
+        <v>18.59702301025391</v>
       </c>
       <c r="C125" t="n">
         <v>22.29000091552734</v>
@@ -3566,7 +3578,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
@@ -3595,7 +3607,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
@@ -3624,11 +3636,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>20.44205665588379</v>
+        <v>20.44205856323242</v>
       </c>
       <c r="C128" t="n">
         <v>24.32333374023438</v>
@@ -3653,7 +3665,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3682,11 +3694,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>20.34224510192871</v>
+        <v>20.34224319458008</v>
       </c>
       <c r="C130" t="n">
         <v>24.04000091552734</v>
@@ -3711,11 +3723,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>19.74991226196289</v>
+        <v>19.74991416931152</v>
       </c>
       <c r="C131" t="n">
         <v>23.34000015258789</v>
@@ -3740,11 +3752,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>19.86556816101074</v>
+        <v>19.86556434631348</v>
       </c>
       <c r="C132" t="n">
         <v>23.4766674041748</v>
@@ -3769,11 +3781,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>19.63559913635254</v>
+        <v>19.63559722900391</v>
       </c>
       <c r="C133" t="n">
         <v>23.04000091552734</v>
@@ -3798,11 +3810,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>18.95948791503906</v>
+        <v>18.9594898223877</v>
       </c>
       <c r="C134" t="n">
         <v>22.24666786193848</v>
@@ -3827,7 +3839,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
@@ -3856,11 +3868,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>20.62703514099121</v>
+        <v>20.62703323364258</v>
       </c>
       <c r="C136" t="n">
         <v>24.02666664123535</v>
@@ -3885,11 +3897,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>21.51416015625</v>
+        <v>21.5141544342041</v>
       </c>
       <c r="C137" t="n">
         <v>25.05999946594238</v>
@@ -3914,11 +3926,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>22.64337730407715</v>
+        <v>22.64338111877441</v>
       </c>
       <c r="C138" t="n">
         <v>26.20000076293945</v>
@@ -3943,11 +3955,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>21.80217170715332</v>
+        <v>21.80217933654785</v>
       </c>
       <c r="C139" t="n">
         <v>25.2266674041748</v>
@@ -3972,11 +3984,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>23.04381370544434</v>
+        <v>23.04381942749023</v>
       </c>
       <c r="C140" t="n">
         <v>26.66333389282227</v>
@@ -4001,11 +4013,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>22.63216018676758</v>
+        <v>22.63216781616211</v>
       </c>
       <c r="C141" t="n">
         <v>26.0233325958252</v>
@@ -4030,7 +4042,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -4059,11 +4071,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>25.31079864501953</v>
+        <v>25.31080055236816</v>
       </c>
       <c r="C143" t="n">
         <v>29.10333251953125</v>
@@ -4088,11 +4100,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>28.18657112121582</v>
+        <v>28.18656921386719</v>
       </c>
       <c r="C144" t="n">
         <v>32.40999984741211</v>
@@ -4117,7 +4129,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -4146,11 +4158,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>31.06575393676758</v>
+        <v>31.06575775146484</v>
       </c>
       <c r="C146" t="n">
         <v>35.53333282470703</v>
@@ -4175,11 +4187,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>26.23103713989258</v>
+        <v>26.23103332519531</v>
       </c>
       <c r="C147" t="n">
         <v>30.00333213806152</v>
@@ -4204,11 +4216,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>26.08253860473633</v>
+        <v>26.0825366973877</v>
       </c>
       <c r="C148" t="n">
         <v>29.65666770935059</v>
@@ -4233,7 +4245,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4262,11 +4274,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>24.34995460510254</v>
+        <v>24.34995269775391</v>
       </c>
       <c r="C150" t="n">
         <v>27.51333236694336</v>
@@ -4291,7 +4303,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
@@ -4320,11 +4332,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>26.32356071472168</v>
+        <v>26.32355690002441</v>
       </c>
       <c r="C152" t="n">
         <v>29.74333381652832</v>
@@ -4349,11 +4361,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>28.44370460510254</v>
+        <v>28.44370651245117</v>
       </c>
       <c r="C153" t="n">
         <v>31.95333290100098</v>
@@ -4378,11 +4390,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>27.86510467529297</v>
+        <v>27.86509895324707</v>
       </c>
       <c r="C154" t="n">
         <v>31.3033332824707</v>
@@ -4407,11 +4419,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>29.75522422790527</v>
+        <v>29.75521659851074</v>
       </c>
       <c r="C155" t="n">
         <v>33.42666625976562</v>
@@ -4436,7 +4448,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
@@ -4465,7 +4477,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -4494,11 +4506,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>28.58997917175293</v>
+        <v>28.58997535705566</v>
       </c>
       <c r="C158" t="n">
         <v>31.94333267211914</v>
@@ -4523,11 +4535,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>29.53273391723633</v>
+        <v>29.53274345397949</v>
       </c>
       <c r="C159" t="n">
         <v>32.99666595458984</v>
@@ -4552,11 +4564,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>29.25371742248535</v>
+        <v>29.25372123718262</v>
       </c>
       <c r="C160" t="n">
         <v>32.5099983215332</v>
@@ -4581,11 +4593,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>30.8464241027832</v>
+        <v>30.8464298248291</v>
       </c>
       <c r="C161" t="n">
         <v>34.27999877929688</v>
@@ -4610,11 +4622,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>30.58813858032227</v>
+        <v>30.588134765625</v>
       </c>
       <c r="C162" t="n">
         <v>33.81333160400391</v>
@@ -4639,7 +4651,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -4668,11 +4680,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>33.28390502929688</v>
+        <v>33.28389739990234</v>
       </c>
       <c r="C164" t="n">
         <v>36.79333114624023</v>
@@ -4697,11 +4709,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>34.62347030639648</v>
+        <v>34.62347412109375</v>
       </c>
       <c r="C165" t="n">
         <v>38.08666610717773</v>
@@ -4726,11 +4738,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>35.96282577514648</v>
+        <v>35.96284484863281</v>
       </c>
       <c r="C166" t="n">
         <v>39.56000137329102</v>
@@ -4755,11 +4767,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>35.53254318237305</v>
+        <v>35.53253936767578</v>
       </c>
       <c r="C167" t="n">
         <v>39.08666610717773</v>
@@ -4784,11 +4796,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>36.08706665039062</v>
+        <v>36.08707046508789</v>
       </c>
       <c r="C168" t="n">
         <v>39.6966667175293</v>
@@ -4813,7 +4825,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4842,7 +4854,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -4871,11 +4883,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>32.77593994140625</v>
+        <v>32.77593612670898</v>
       </c>
       <c r="C171" t="n">
         <v>35.89333343505859</v>
@@ -4900,11 +4912,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>34.73699951171875</v>
+        <v>34.73698806762695</v>
       </c>
       <c r="C172" t="n">
         <v>37.87333297729492</v>
@@ -4929,11 +4941,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>37.16143417358398</v>
+        <v>37.16143035888672</v>
       </c>
       <c r="C173" t="n">
         <v>40.51666641235352</v>
@@ -4958,7 +4970,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -4987,11 +4999,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>36.7813720703125</v>
+        <v>36.78136825561523</v>
       </c>
       <c r="C175" t="n">
         <v>39.92666625976562</v>
@@ -5016,11 +5028,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>39.73542785644531</v>
+        <v>39.73543167114258</v>
       </c>
       <c r="C176" t="n">
         <v>43.13333129882812</v>
@@ -5045,7 +5057,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -5074,11 +5086,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>43.13940048217773</v>
+        <v>43.139404296875</v>
       </c>
       <c r="C178" t="n">
         <v>46.63666534423828</v>
@@ -5103,11 +5115,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>42.78173446655273</v>
+        <v>42.78174209594727</v>
       </c>
       <c r="C179" t="n">
         <v>46.25</v>
@@ -5132,7 +5144,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -5161,11 +5173,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>44.60922622680664</v>
+        <v>44.60922241210938</v>
       </c>
       <c r="C181" t="n">
         <v>48.04999923706055</v>
@@ -5190,7 +5202,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -5219,11 +5231,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>40.20555114746094</v>
+        <v>40.20555877685547</v>
       </c>
       <c r="C183" t="n">
         <v>43.30666732788086</v>
@@ -5248,11 +5260,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>42.20998764038086</v>
+        <v>42.20998382568359</v>
       </c>
       <c r="C184" t="n">
         <v>45.27666854858398</v>
@@ -5277,7 +5289,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -5306,11 +5318,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>44.31000900268555</v>
+        <v>44.31000137329102</v>
       </c>
       <c r="C186" t="n">
         <v>47.34333419799805</v>
@@ -5335,11 +5347,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>43.99490737915039</v>
+        <v>43.99491500854492</v>
       </c>
       <c r="C187" t="n">
         <v>47.00666809082031</v>
@@ -5364,7 +5376,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5393,11 +5405,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>46.37372970581055</v>
+        <v>46.37373352050781</v>
       </c>
       <c r="C189" t="n">
         <v>49.36666870117188</v>
@@ -5422,11 +5434,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>43.64328384399414</v>
+        <v>43.64328765869141</v>
       </c>
       <c r="C190" t="n">
         <v>46.45999908447266</v>
@@ -5451,11 +5463,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>46.78704833984375</v>
+        <v>46.78705215454102</v>
       </c>
       <c r="C191" t="n">
         <v>49.80666732788086</v>
@@ -5480,11 +5492,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>44.03468322753906</v>
+        <v>44.03469085693359</v>
       </c>
       <c r="C192" t="n">
         <v>46.87666702270508</v>
@@ -5509,11 +5521,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>45.48838806152344</v>
+        <v>45.4883918762207</v>
       </c>
       <c r="C193" t="n">
         <v>48.22999954223633</v>
@@ -5538,11 +5550,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>43.95420074462891</v>
+        <v>43.95419311523438</v>
       </c>
       <c r="C194" t="n">
         <v>46.60333251953125</v>
@@ -5567,7 +5579,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
@@ -5596,11 +5608,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>46.99932861328125</v>
+        <v>46.99932098388672</v>
       </c>
       <c r="C196" t="n">
         <v>49.63999938964844</v>
@@ -5625,11 +5637,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>48.2838249206543</v>
+        <v>48.2838134765625</v>
       </c>
       <c r="C197" t="n">
         <v>50.99666595458984</v>
@@ -5654,11 +5666,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>40.74333190917969</v>
+        <v>40.74333572387695</v>
       </c>
       <c r="C198" t="n">
         <v>42.87666702270508</v>
@@ -5683,11 +5695,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>38.51025772094727</v>
+        <v>38.51026153564453</v>
       </c>
       <c r="C199" t="n">
         <v>40.52666854858398</v>
@@ -5712,11 +5724,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>41.82662200927734</v>
+        <v>41.82660675048828</v>
       </c>
       <c r="C200" t="n">
         <v>44.01666641235352</v>
@@ -5741,11 +5753,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>42.16785049438477</v>
+        <v>42.16785430908203</v>
       </c>
       <c r="C201" t="n">
         <v>44.18333435058594</v>
@@ -5770,11 +5782,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>41.26118087768555</v>
+        <v>41.26118850708008</v>
       </c>
       <c r="C202" t="n">
         <v>43.23333358764648</v>
@@ -5799,7 +5811,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5828,11 +5840,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>48.48904800415039</v>
+        <v>48.48904037475586</v>
       </c>
       <c r="C204" t="n">
         <v>50.80666732788086</v>
@@ -5857,11 +5869,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>45.27739334106445</v>
+        <v>45.27739715576172</v>
       </c>
       <c r="C205" t="n">
         <v>47.26333236694336</v>
@@ -5886,7 +5898,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5915,11 +5927,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>45.38595581054688</v>
+        <v>45.38596725463867</v>
       </c>
       <c r="C207" t="n">
         <v>47.37666702270508</v>
@@ -5944,11 +5956,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>47.27776718139648</v>
+        <v>47.27776336669922</v>
       </c>
       <c r="C208" t="n">
         <v>49.15000152587891</v>
@@ -5973,11 +5985,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>48.40640640258789</v>
+        <v>48.40640258789062</v>
       </c>
       <c r="C209" t="n">
         <v>50.32333374023438</v>
@@ -6002,11 +6014,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>47.27068328857422</v>
+        <v>47.27069091796875</v>
       </c>
       <c r="C210" t="n">
         <v>48.95666885375977</v>
@@ -6031,11 +6043,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>50.58899688720703</v>
+        <v>50.58899307250977</v>
       </c>
       <c r="C211" t="n">
         <v>52.39333343505859</v>
@@ -6060,11 +6072,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>51.45156860351562</v>
+        <v>51.45157241821289</v>
       </c>
       <c r="C212" t="n">
         <v>53.28666687011719</v>
@@ -6089,7 +6101,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6118,11 +6130,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>51.6570930480957</v>
+        <v>51.65708541870117</v>
       </c>
       <c r="C214" t="n">
         <v>53.31000137329102</v>
@@ -6147,11 +6159,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>52.7811279296875</v>
+        <v>52.78112030029297</v>
       </c>
       <c r="C215" t="n">
         <v>54.47000122070312</v>
@@ -6176,7 +6188,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6205,11 +6217,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>51.10977172851562</v>
+        <v>51.10976791381836</v>
       </c>
       <c r="C217" t="n">
         <v>52.54999923706055</v>
@@ -6234,7 +6246,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6263,11 +6275,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>57.00369262695312</v>
+        <v>57.00368881225586</v>
       </c>
       <c r="C219" t="n">
         <v>58.61000061035156</v>
@@ -6292,7 +6304,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6321,11 +6333,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>57.92000198364258</v>
+        <v>57.92000579833984</v>
       </c>
       <c r="C221" t="n">
         <v>59.34999847412109</v>
@@ -6350,11 +6362,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>64.39769744873047</v>
+        <v>64.397705078125</v>
       </c>
       <c r="C222" t="n">
         <v>65.76000213623047</v>
@@ -6379,7 +6391,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6408,11 +6420,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>67.21802520751953</v>
+        <v>67.21804046630859</v>
       </c>
       <c r="C224" t="n">
         <v>68.63999938964844</v>
@@ -6437,11 +6449,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>75.84564971923828</v>
+        <v>75.84566497802734</v>
       </c>
       <c r="C225" t="n">
         <v>77.23000335693359</v>
@@ -6466,11 +6478,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>79.30256652832031</v>
+        <v>79.30255889892578</v>
       </c>
       <c r="C226" t="n">
         <v>80.75</v>
@@ -6495,11 +6507,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>80.48104095458984</v>
+        <v>80.48105621337891</v>
       </c>
       <c r="C227" t="n">
         <v>81.94999694824219</v>
@@ -6524,7 +6536,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6553,11 +6565,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>88.92706298828125</v>
+        <v>88.92707824707031</v>
       </c>
       <c r="C229" t="n">
         <v>90.34999847412109</v>
@@ -6582,11 +6594,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>96.61408233642578</v>
+        <v>96.61406707763672</v>
       </c>
       <c r="C230" t="n">
         <v>98.16000366210938</v>
@@ -6611,7 +6623,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6640,11 +6652,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>86.64466857910156</v>
+        <v>86.64467620849609</v>
       </c>
       <c r="C232" t="n">
         <v>87.79000091552734</v>
@@ -6669,7 +6681,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6698,11 +6710,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>97.66764068603516</v>
+        <v>97.66765594482422</v>
       </c>
       <c r="C234" t="n">
         <v>98.72000122070312</v>
@@ -6727,7 +6739,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6756,11 +6768,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>96.93553161621094</v>
+        <v>96.93553924560547</v>
       </c>
       <c r="C236" t="n">
         <v>97.98000335693359</v>
@@ -6785,7 +6797,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6814,7 +6826,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6843,7 +6855,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6872,7 +6884,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6901,11 +6913,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>110.7050170898438</v>
+        <v>110.7050247192383</v>
       </c>
       <c r="C241" t="n">
         <v>111.4100036621094</v>
@@ -6930,11 +6942,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>118.3861083984375</v>
+        <v>118.386100769043</v>
       </c>
       <c r="C242" t="n">
         <v>119.1399993896484</v>
@@ -6959,7 +6971,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6988,7 +7000,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7017,11 +7029,11 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>131.3641967773438</v>
+        <v>131.3642120361328</v>
       </c>
       <c r="C245" t="n">
         <v>131.9299926757812</v>
@@ -7046,7 +7058,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7075,7 +7087,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7104,7 +7116,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7133,7 +7145,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7162,32 +7174,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>110.5299987792969</v>
+        <v>107.5899963378906</v>
       </c>
       <c r="C250" t="n">
-        <v>110.5299987792969</v>
+        <v>107.5899963378906</v>
       </c>
       <c r="D250" t="n">
-        <v>354656800</v>
+        <v>380868700</v>
       </c>
       <c r="E250" t="n">
         <v>2.76</v>
       </c>
       <c r="F250" t="n">
-        <v>40.04710100699162</v>
+        <v>38.9818827311198</v>
       </c>
       <c r="G250" t="n">
         <v>7933746241</v>
       </c>
       <c r="H250" t="n">
-        <v>876916962332.9812</v>
+        <v>853591729014.9435</v>
       </c>
       <c r="I250" t="n">
-        <v>0.04470231202596388</v>
+        <v>0.04800616107832482</v>
       </c>
     </row>
   </sheetData>
@@ -7219,75 +7231,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39569</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39660</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40065</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7323,13 +7335,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39661</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39752</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40155</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7365,13 +7377,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39845</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39933</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40333</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7407,13 +7419,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39934</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40065</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7449,13 +7461,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40026</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40117</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40155</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7491,13 +7503,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40118</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40632</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7524,7 +7536,7 @@
       <c r="I7" t="n">
         <v>1.246666666666667</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40632</v>
       </c>
       <c r="K7" t="n">
@@ -7537,13 +7549,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40210</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40333</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7570,7 +7582,7 @@
       <c r="I8" t="n">
         <v>1.283333333333333</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40632</v>
       </c>
       <c r="K8" t="n">
@@ -7583,13 +7595,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40299</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40390</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40422</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7616,7 +7628,7 @@
       <c r="I9" t="n">
         <v>1.313333333333333</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40632</v>
       </c>
       <c r="K9" t="n">
@@ -7629,13 +7641,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40391</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40482</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40518</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7662,7 +7674,7 @@
       <c r="I10" t="n">
         <v>1.35</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40632</v>
       </c>
       <c r="K10" t="n">
@@ -7675,13 +7687,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40483</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40632</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7708,7 +7720,7 @@
       <c r="I11" t="n">
         <v>1.5</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40632</v>
       </c>
       <c r="K11" t="n">
@@ -7721,13 +7733,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40575</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40663</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40697</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7754,7 +7766,7 @@
       <c r="I12" t="n">
         <v>1.53</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40697</v>
       </c>
       <c r="K12" t="n">
@@ -7767,13 +7779,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40664</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40755</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7800,7 +7812,7 @@
       <c r="I13" t="n">
         <v>1.57</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="K13" t="n">
@@ -7813,13 +7825,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40756</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40885</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7846,7 +7858,7 @@
       <c r="I14" t="n">
         <v>1.573333333333333</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40885</v>
       </c>
       <c r="K14" t="n">
@@ -7859,13 +7871,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40848</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40995</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7892,7 +7904,7 @@
       <c r="I15" t="n">
         <v>1.506666666666667</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40995</v>
       </c>
       <c r="K15" t="n">
@@ -7905,13 +7917,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40940</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41029</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41061</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7938,7 +7950,7 @@
       <c r="I16" t="n">
         <v>1.546666666666667</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41061</v>
       </c>
       <c r="K16" t="n">
@@ -7951,13 +7963,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41030</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41158</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7984,7 +7996,7 @@
       <c r="I17" t="n">
         <v>1.576666666666666</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41158</v>
       </c>
       <c r="K17" t="n">
@@ -7997,13 +8009,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41122</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41213</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41247</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8030,7 +8042,7 @@
       <c r="I18" t="n">
         <v>1.616666666666667</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41247</v>
       </c>
       <c r="K18" t="n">
@@ -8043,13 +8055,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41214</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41359</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8076,7 +8088,7 @@
       <c r="I19" t="n">
         <v>1.673333333333333</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41359</v>
       </c>
       <c r="K19" t="n">
@@ -8089,13 +8101,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41306</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41394</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41432</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8122,7 +8134,7 @@
       <c r="I20" t="n">
         <v>1.69</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41432</v>
       </c>
       <c r="K20" t="n">
@@ -8135,13 +8147,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41395</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41522</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8168,7 +8180,7 @@
       <c r="I21" t="n">
         <v>1.71</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41522</v>
       </c>
       <c r="K21" t="n">
@@ -8181,13 +8193,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41487</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41614</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8214,7 +8226,7 @@
       <c r="I22" t="n">
         <v>1.73</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41614</v>
       </c>
       <c r="K22" t="n">
@@ -8227,13 +8239,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41579</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41719</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8260,7 +8272,7 @@
       <c r="I23" t="n">
         <v>1.626666666666666</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41719</v>
       </c>
       <c r="K23" t="n">
@@ -8273,13 +8285,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41671</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41759</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41796</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8306,7 +8318,7 @@
       <c r="I24" t="n">
         <v>1.616666666666667</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41796</v>
       </c>
       <c r="K24" t="n">
@@ -8319,13 +8331,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41760</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41851</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41887</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8352,7 +8364,7 @@
       <c r="I25" t="n">
         <v>1.623333333333334</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41887</v>
       </c>
       <c r="K25" t="n">
@@ -8365,13 +8377,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41852</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41974</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8398,7 +8410,7 @@
       <c r="I26" t="n">
         <v>1.626666666666667</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41974</v>
       </c>
       <c r="K26" t="n">
@@ -8411,13 +8423,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41944</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42095</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8444,7 +8456,7 @@
       <c r="I27" t="n">
         <v>1.683333333333333</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42095</v>
       </c>
       <c r="K27" t="n">
@@ -8457,13 +8469,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42036</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42160</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8490,7 +8502,7 @@
       <c r="I28" t="n">
         <v>1.656666666666667</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42160</v>
       </c>
       <c r="K28" t="n">
@@ -8503,13 +8515,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42125</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42256</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8536,7 +8548,7 @@
       <c r="I29" t="n">
         <v>1.596666666666667</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42256</v>
       </c>
       <c r="K29" t="n">
@@ -8549,13 +8561,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42217</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42308</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42340</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8582,7 +8594,7 @@
       <c r="I30" t="n">
         <v>1.556666666666667</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42340</v>
       </c>
       <c r="K30" t="n">
@@ -8595,13 +8607,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42309</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42459</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8628,7 +8640,7 @@
       <c r="I31" t="n">
         <v>1.523333333333333</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42459</v>
       </c>
       <c r="K31" t="n">
@@ -8641,13 +8653,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42401</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42490</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42524</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8674,7 +8686,7 @@
       <c r="I32" t="n">
         <v>1.506666666666667</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42524</v>
       </c>
       <c r="K32" t="n">
@@ -8687,13 +8699,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42491</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42582</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8720,7 +8732,7 @@
       <c r="I33" t="n">
         <v>1.55</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="K33" t="n">
@@ -8733,13 +8745,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42583</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42705</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8766,7 +8778,7 @@
       <c r="I34" t="n">
         <v>1.533333333333333</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42705</v>
       </c>
       <c r="K34" t="n">
@@ -8779,13 +8791,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42675</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8812,7 +8824,7 @@
       <c r="I35" t="n">
         <v>1.463333333333333</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="K35" t="n">
@@ -8825,13 +8837,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42767</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42855</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42888</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8858,7 +8870,7 @@
       <c r="I36" t="n">
         <v>1.47</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42888</v>
       </c>
       <c r="K36" t="n">
@@ -8871,13 +8883,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42856</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42947</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8904,7 +8916,7 @@
       <c r="I37" t="n">
         <v>1.386666666666667</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="K37" t="n">
@@ -8917,13 +8929,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42948</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43039</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8950,7 +8962,7 @@
       <c r="I38" t="n">
         <v>1.253333333333333</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="K38" t="n">
@@ -8963,13 +8975,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43040</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43189</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8996,7 +9008,7 @@
       <c r="I39" t="n">
         <v>1.09</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43189</v>
       </c>
       <c r="K39" t="n">
@@ -9009,13 +9021,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43132</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43220</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43255</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9042,7 +9054,7 @@
       <c r="I40" t="n">
         <v>0.9966666666666666</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43255</v>
       </c>
       <c r="K40" t="n">
@@ -9055,13 +9067,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43221</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43312</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43349</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9088,7 +9100,7 @@
       <c r="I41" t="n">
         <v>0.58</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43349</v>
       </c>
       <c r="K41" t="n">
@@ -9101,13 +9113,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43313</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43404</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9134,7 +9146,7 @@
       <c r="I42" t="n">
         <v>0.5800000000000001</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="K42" t="n">
@@ -9147,13 +9159,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43405</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43552</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9180,7 +9192,7 @@
       <c r="I43" t="n">
         <v>0.76</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43552</v>
       </c>
       <c r="K43" t="n">
@@ -9193,13 +9205,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43497</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43585</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43623</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9226,7 +9238,7 @@
       <c r="I44" t="n">
         <v>0.9633333333333334</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43623</v>
       </c>
       <c r="K44" t="n">
@@ -9239,13 +9251,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43586</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43677</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43714</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9272,7 +9284,7 @@
       <c r="I45" t="n">
         <v>1.48</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43714</v>
       </c>
       <c r="K45" t="n">
@@ -9285,13 +9297,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43678</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43769</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43803</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9318,7 +9330,7 @@
       <c r="I46" t="n">
         <v>1.67</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43803</v>
       </c>
       <c r="K46" t="n">
@@ -9331,13 +9343,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43770</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43910</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9364,7 +9376,7 @@
       <c r="I47" t="n">
         <v>1.73</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43910</v>
       </c>
       <c r="K47" t="n">
@@ -9377,13 +9389,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43862</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43951</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43985</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9410,7 +9422,7 @@
       <c r="I48" t="n">
         <v>1.753333333333333</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43985</v>
       </c>
       <c r="K48" t="n">
@@ -9423,13 +9435,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43952</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44076</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9456,7 +9468,7 @@
       <c r="I49" t="n">
         <v>2.09</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44076</v>
       </c>
       <c r="K49" t="n">
@@ -9469,13 +9481,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44044</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44135</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44167</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9502,7 +9514,7 @@
       <c r="I50" t="n">
         <v>2.306666666666667</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44167</v>
       </c>
       <c r="K50" t="n">
@@ -9515,13 +9527,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44136</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44274</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9548,7 +9560,7 @@
       <c r="I51" t="n">
         <v>1.583333333333333</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44274</v>
       </c>
       <c r="K51" t="n">
@@ -9561,13 +9573,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44228</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44316</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44351</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9594,7 +9606,7 @@
       <c r="I52" t="n">
         <v>1.44</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44351</v>
       </c>
       <c r="K52" t="n">
@@ -9607,13 +9619,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44317</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44408</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44441</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9640,7 +9652,7 @@
       <c r="I53" t="n">
         <v>1.19</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44441</v>
       </c>
       <c r="K53" t="n">
@@ -9653,13 +9665,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44409</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44500</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9686,7 +9698,7 @@
       <c r="I54" t="n">
         <v>0.96</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="K54" t="n">
@@ -9699,13 +9711,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44501</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44638</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9732,7 +9744,7 @@
       <c r="I55" t="n">
         <v>1.623333333333333</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44638</v>
       </c>
       <c r="K55" t="n">
@@ -9745,13 +9757,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44593</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44681</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44715</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9778,7 +9790,7 @@
       <c r="I56" t="n">
         <v>1.546666666666667</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44715</v>
       </c>
       <c r="K56" t="n">
@@ -9791,13 +9803,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44682</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44773</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44806</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9824,7 +9836,7 @@
       <c r="I57" t="n">
         <v>1.666666666666666</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44806</v>
       </c>
       <c r="K57" t="n">
@@ -9837,13 +9849,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44774</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44865</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9870,7 +9882,7 @@
       <c r="I58" t="n">
         <v>1.076666666666666</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="K58" t="n">
@@ -9883,13 +9895,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44866</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45002</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9916,7 +9928,7 @@
       <c r="I59" t="n">
         <v>1.423333333333333</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45002</v>
       </c>
       <c r="K59" t="n">
@@ -9929,13 +9941,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44958</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45046</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45079</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9962,7 +9974,7 @@
       <c r="I60" t="n">
         <v>1.383333333333333</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45079</v>
       </c>
       <c r="K60" t="n">
@@ -9975,13 +9987,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45047</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10008,7 +10020,7 @@
       <c r="I61" t="n">
         <v>1.73</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="K61" t="n">
@@ -10021,13 +10033,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45139</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45230</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10054,7 +10066,7 @@
       <c r="I62" t="n">
         <v>2.006666666666666</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="K62" t="n">
@@ -10067,13 +10079,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45231</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45366</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10100,7 +10112,7 @@
       <c r="I63" t="n">
         <v>1.91</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45366</v>
       </c>
       <c r="K63" t="n">
@@ -10113,13 +10125,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45323</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45412</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45450</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10146,7 +10158,7 @@
       <c r="I64" t="n">
         <v>2.333333333333333</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45450</v>
       </c>
       <c r="K64" t="n">
@@ -10159,13 +10171,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45413</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45504</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45534</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10192,7 +10204,7 @@
       <c r="I65" t="n">
         <v>1.92</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45534</v>
       </c>
       <c r="K65" t="n">
@@ -10205,13 +10217,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45505</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45596</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45632</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10238,7 +10250,7 @@
       <c r="I66" t="n">
         <v>2.433333333333333</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45632</v>
       </c>
       <c r="K66" t="n">
@@ -10251,13 +10263,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45597</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45730</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10284,7 +10296,7 @@
       <c r="I67" t="n">
         <v>2.41</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45730</v>
       </c>
       <c r="K67" t="n">
@@ -10297,13 +10309,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45689</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45777</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45814</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10330,7 +10342,7 @@
       <c r="I68" t="n">
         <v>2.34</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45814</v>
       </c>
       <c r="K68" t="n">
@@ -10343,13 +10355,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45778</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45869</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10376,7 +10388,7 @@
       <c r="I69" t="n">
         <v>2.66</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="K69" t="n">
@@ -10389,13 +10401,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45961</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45994</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10422,7 +10434,7 @@
       <c r="I70" t="n">
         <v>2.86</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45994</v>
       </c>
       <c r="K70" t="n">
@@ -10435,13 +10447,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45962</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46094</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10468,7 +10480,7 @@
       <c r="I71" t="n">
         <v>2.73</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46094</v>
       </c>
       <c r="K71" t="n">
@@ -10481,13 +10493,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46054</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46171</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10514,7 +10526,7 @@
       <c r="I72" t="n">
         <v>2.84</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46171</v>
       </c>
       <c r="K72" t="n">
@@ -10527,13 +10539,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10560,7 +10572,7 @@
       <c r="I73" t="n">
         <v>2.76</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="K73" t="n">
@@ -10597,52 +10609,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40060</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40065</v>
       </c>
       <c r="C2" t="n">
@@ -10671,10 +10683,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40150</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40155</v>
       </c>
       <c r="C3" t="n">
@@ -10703,10 +10715,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40263</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40267</v>
       </c>
       <c r="C4" t="n">
@@ -10735,10 +10747,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40330</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40333</v>
       </c>
       <c r="C5" t="n">
@@ -10767,10 +10779,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40417</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40422</v>
       </c>
       <c r="C6" t="n">
@@ -10799,10 +10811,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40512</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40518</v>
       </c>
       <c r="C7" t="n">
@@ -10831,10 +10843,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40623</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40632</v>
       </c>
       <c r="C8" t="n">
@@ -10863,10 +10875,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40694</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40697</v>
       </c>
       <c r="C9" t="n">
@@ -10895,10 +10907,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40784</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="C10" t="n">
@@ -10927,10 +10939,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40883</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40885</v>
       </c>
       <c r="C11" t="n">
@@ -10959,10 +10971,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40990</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40995</v>
       </c>
       <c r="C12" t="n">
@@ -10991,10 +11003,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41058</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41061</v>
       </c>
       <c r="C13" t="n">
@@ -11023,10 +11035,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41152</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41158</v>
       </c>
       <c r="C14" t="n">
@@ -11055,10 +11067,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41243</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41247</v>
       </c>
       <c r="C15" t="n">
@@ -11087,10 +11099,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41355</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41359</v>
       </c>
       <c r="C16" t="n">
@@ -11119,10 +11131,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41429</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41432</v>
       </c>
       <c r="C17" t="n">
@@ -11151,10 +11163,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41520</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41522</v>
       </c>
       <c r="C18" t="n">
@@ -11183,10 +11195,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41564</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41568</v>
       </c>
       <c r="C19" t="n">
@@ -11215,10 +11227,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41612</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41614</v>
       </c>
       <c r="C20" t="n">
@@ -11247,10 +11259,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41716</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41719</v>
       </c>
       <c r="C21" t="n">
@@ -11279,10 +11291,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41794</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41796</v>
       </c>
       <c r="C22" t="n">
@@ -11311,10 +11323,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41885</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41887</v>
       </c>
       <c r="C23" t="n">
@@ -11343,10 +11355,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41969</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41974</v>
       </c>
       <c r="C24" t="n">
@@ -11375,10 +11387,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42093</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42095</v>
       </c>
       <c r="C25" t="n">
@@ -11407,10 +11419,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42158</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42160</v>
       </c>
       <c r="C26" t="n">
@@ -11439,10 +11451,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42255</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42256</v>
       </c>
       <c r="C27" t="n">
@@ -11471,10 +11483,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42338</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42340</v>
       </c>
       <c r="C28" t="n">
@@ -11503,10 +11515,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42457</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42459</v>
       </c>
       <c r="C29" t="n">
@@ -11535,10 +11547,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42522</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42524</v>
       </c>
       <c r="C30" t="n">
@@ -11567,10 +11579,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42611</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="C31" t="n">
@@ -11599,10 +11611,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42702</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42705</v>
       </c>
       <c r="C32" t="n">
@@ -11631,10 +11643,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42823</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="C33" t="n">
@@ -11663,10 +11675,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42886</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42888</v>
       </c>
       <c r="C34" t="n">
@@ -11695,10 +11707,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42976</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="C35" t="n">
@@ -11727,10 +11739,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43068</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="C36" t="n">
@@ -11759,10 +11771,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43187</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43189</v>
       </c>
       <c r="C37" t="n">
@@ -11791,10 +11803,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43251</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43255</v>
       </c>
       <c r="C38" t="n">
@@ -11823,10 +11835,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43347</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43349</v>
       </c>
       <c r="C39" t="n">
@@ -11855,10 +11867,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43432</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="C40" t="n">
@@ -11887,10 +11899,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43550</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43552</v>
       </c>
       <c r="C41" t="n">
@@ -11919,10 +11931,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43621</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43623</v>
       </c>
       <c r="C42" t="n">
@@ -11951,10 +11963,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43712</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43714</v>
       </c>
       <c r="C43" t="n">
@@ -11983,10 +11995,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43801</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43803</v>
       </c>
       <c r="C44" t="n">
@@ -12015,10 +12027,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43908</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43910</v>
       </c>
       <c r="C45" t="n">
@@ -12047,10 +12059,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43983</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43985</v>
       </c>
       <c r="C46" t="n">
@@ -12079,10 +12091,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44074</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44076</v>
       </c>
       <c r="C47" t="n">
@@ -12111,10 +12123,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44165</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44167</v>
       </c>
       <c r="C48" t="n">
@@ -12143,10 +12155,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44272</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44274</v>
       </c>
       <c r="C49" t="n">
@@ -12175,10 +12187,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44349</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44351</v>
       </c>
       <c r="C50" t="n">
@@ -12207,10 +12219,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44439</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44441</v>
       </c>
       <c r="C51" t="n">
@@ -12239,10 +12251,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44529</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="C52" t="n">
@@ -12271,10 +12283,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44636</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44638</v>
       </c>
       <c r="C53" t="n">
@@ -12303,10 +12315,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44713</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44715</v>
       </c>
       <c r="C54" t="n">
@@ -12335,10 +12347,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44804</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44806</v>
       </c>
       <c r="C55" t="n">
@@ -12367,10 +12379,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44894</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="C56" t="n">
@@ -12399,10 +12411,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45000</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45002</v>
       </c>
       <c r="C57" t="n">
@@ -12431,10 +12443,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45077</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45079</v>
       </c>
       <c r="C58" t="n">
@@ -12463,10 +12475,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45168</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="C59" t="n">
@@ -12495,10 +12507,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45258</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="C60" t="n">
@@ -12527,10 +12539,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45364</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45366</v>
       </c>
       <c r="C61" t="n">
@@ -12559,10 +12571,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45448</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45450</v>
       </c>
       <c r="C62" t="n">
@@ -12591,10 +12603,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45532</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45534</v>
       </c>
       <c r="C63" t="n">
@@ -12623,10 +12635,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45630</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45632</v>
       </c>
       <c r="C64" t="n">
@@ -12655,10 +12667,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45728</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45730</v>
       </c>
       <c r="C65" t="n">
@@ -12687,10 +12699,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45812</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45814</v>
       </c>
       <c r="C66" t="n">
@@ -12719,10 +12731,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45896</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="C67" t="n">
@@ -12751,10 +12763,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45993</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45994</v>
       </c>
       <c r="C68" t="n">
@@ -12783,10 +12795,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46092</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46094</v>
       </c>
       <c r="C69" t="n">
@@ -12815,10 +12827,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46169</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46171</v>
       </c>
       <c r="C70" t="n">
@@ -12847,10 +12859,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46260</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="C71" t="n">
@@ -12897,12 +12909,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/WMT.xlsx
+++ b/salidas/empresas/WMT.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>10.18526458740234</v>
+        <v>10.18526935577393</v>
       </c>
       <c r="C2" t="n">
         <v>15.36999988555908</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>10.0196008682251</v>
+        <v>10.01959896087646</v>
       </c>
       <c r="C3" t="n">
         <v>15.11999988555908</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>10.47351551055908</v>
+        <v>10.47351169586182</v>
       </c>
       <c r="C4" t="n">
         <v>15.74666690826416</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>9.983537673950195</v>
+        <v>9.983534812927246</v>
       </c>
       <c r="C5" t="n">
         <v>15.01000022888184</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>10.77945232391357</v>
+        <v>10.77945327758789</v>
       </c>
       <c r="C6" t="n">
         <v>16.14999961853027</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>10.71715927124023</v>
+        <v>10.71715545654297</v>
       </c>
       <c r="C7" t="n">
         <v>16.05666732788086</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>9.987241744995117</v>
+        <v>9.987242698669434</v>
       </c>
       <c r="C9" t="n">
         <v>14.90666675567627</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>11.01455211639404</v>
+        <v>11.01455116271973</v>
       </c>
       <c r="C10" t="n">
         <v>16.44000053405762</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>11.00561428070068</v>
+        <v>11.00561618804932</v>
       </c>
       <c r="C11" t="n">
         <v>16.42666625976562</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>10.35139942169189</v>
+        <v>10.35139465332031</v>
       </c>
       <c r="C13" t="n">
         <v>15.39333343505859</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>10.68986701965332</v>
+        <v>10.689866065979</v>
       </c>
       <c r="C14" t="n">
         <v>15.89666652679443</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>10.8288402557373</v>
+        <v>10.82884311676025</v>
       </c>
       <c r="C15" t="n">
         <v>16.10333251953125</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>10.57437038421631</v>
+        <v>10.57436847686768</v>
       </c>
       <c r="C16" t="n">
         <v>15.64999961853027</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>10.79283905029297</v>
+        <v>10.79284000396729</v>
       </c>
       <c r="C17" t="n">
         <v>15.97333335876465</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>10.77052783966064</v>
+        <v>10.77052688598633</v>
       </c>
       <c r="C18" t="n">
         <v>15.86666679382324</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>10.88592529296875</v>
+        <v>10.88592338562012</v>
       </c>
       <c r="C19" t="n">
         <v>16.03666687011719</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>10.39717960357666</v>
+        <v>10.39717864990234</v>
       </c>
       <c r="C20" t="n">
         <v>15.31666660308838</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>9.922039985656738</v>
+        <v>9.922041893005371</v>
       </c>
       <c r="C21" t="n">
         <v>14.54333305358887</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>10.28135299682617</v>
+        <v>10.28135395050049</v>
       </c>
       <c r="C23" t="n">
         <v>15.06999969482422</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>10.89309978485107</v>
+        <v>10.89309787750244</v>
       </c>
       <c r="C24" t="n">
         <v>15.96666717529297</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>10.85767269134521</v>
+        <v>10.8576717376709</v>
       </c>
       <c r="C25" t="n">
         <v>15.84333324432373</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>11.59096050262451</v>
+        <v>11.59095668792725</v>
       </c>
       <c r="C26" t="n">
         <v>16.91333389282227</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>11.32825469970703</v>
+        <v>11.32825565338135</v>
       </c>
       <c r="C27" t="n">
         <v>16.53000068664551</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>12.09140014648438</v>
+        <v>12.09139442443848</v>
       </c>
       <c r="C28" t="n">
         <v>17.55999946594238</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>13.30788230895996</v>
+        <v>13.30788516998291</v>
       </c>
       <c r="C29" t="n">
         <v>19.32666778564453</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>13.30871200561523</v>
+        <v>13.30871295928955</v>
       </c>
       <c r="C30" t="n">
         <v>19.24666786193848</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>12.9537525177002</v>
+        <v>12.95374393463135</v>
       </c>
       <c r="C31" t="n">
         <v>18.73333358764648</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>13.51154518127441</v>
+        <v>13.51154899597168</v>
       </c>
       <c r="C32" t="n">
         <v>19.54000091552734</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>13.67017459869385</v>
+        <v>13.67017269134521</v>
       </c>
       <c r="C33" t="n">
         <v>19.69000053405762</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>13.85994434356689</v>
+        <v>13.85994625091553</v>
       </c>
       <c r="C34" t="n">
         <v>19.96333312988281</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>12.91573810577393</v>
+        <v>12.91574096679688</v>
       </c>
       <c r="C35" t="n">
         <v>18.60333251953125</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>12.93193912506104</v>
+        <v>12.9319429397583</v>
       </c>
       <c r="C36" t="n">
         <v>18.62666702270508</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>11.44458198547363</v>
+        <v>11.44458389282227</v>
       </c>
       <c r="C39" t="n">
         <v>16.41333389282227</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>12.17762660980225</v>
+        <v>12.17762279510498</v>
       </c>
       <c r="C40" t="n">
         <v>17.36666679382324</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>11.78027820587158</v>
+        <v>11.78027629852295</v>
       </c>
       <c r="C41" t="n">
         <v>16.79999923706055</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>11.6887035369873</v>
+        <v>11.68869876861572</v>
       </c>
       <c r="C42" t="n">
         <v>16.57999992370605</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>11.38320922851562</v>
+        <v>11.38320827484131</v>
       </c>
       <c r="C43" t="n">
         <v>16.14666748046875</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>11.72160243988037</v>
+        <v>11.721604347229</v>
       </c>
       <c r="C44" t="n">
         <v>16.62666702270508</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>12.01982498168945</v>
+        <v>12.01982402801514</v>
       </c>
       <c r="C45" t="n">
         <v>16.95666694641113</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>11.59923362731934</v>
+        <v>11.59923458099365</v>
       </c>
       <c r="C46" t="n">
         <v>16.36333274841309</v>
@@ -1359,7 +1359,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>11.73864269256592</v>
+        <v>11.73864555358887</v>
       </c>
       <c r="C47" t="n">
         <v>16.55999946594238</v>
@@ -1384,7 +1384,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>12.88934898376465</v>
+        <v>12.8893518447876</v>
       </c>
       <c r="C48" t="n">
         <v>18.1833324432373</v>
@@ -1409,7 +1409,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>12.69312763214111</v>
+        <v>12.6931209564209</v>
       </c>
       <c r="C49" t="n">
         <v>17.8166675567627</v>
@@ -1434,7 +1434,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>12.68838024139404</v>
+        <v>12.68837547302246</v>
       </c>
       <c r="C50" t="n">
         <v>17.80999946594238</v>
@@ -1459,7 +1459,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>12.84036159515381</v>
+        <v>12.84035778045654</v>
       </c>
       <c r="C51" t="n">
         <v>18.0233325958252</v>
@@ -1509,7 +1509,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>12.81004238128662</v>
+        <v>12.81004428863525</v>
       </c>
       <c r="C53" t="n">
         <v>17.8799991607666</v>
@@ -1534,7 +1534,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>12.14464378356934</v>
+        <v>12.14463996887207</v>
       </c>
       <c r="C54" t="n">
         <v>16.85333251953125</v>
@@ -1584,7 +1584,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>12.29597091674805</v>
+        <v>12.2959680557251</v>
       </c>
       <c r="C56" t="n">
         <v>17.06333351135254</v>
@@ -1609,7 +1609,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>12.11404800415039</v>
+        <v>12.11404323577881</v>
       </c>
       <c r="C57" t="n">
         <v>16.71333312988281</v>
@@ -1634,7 +1634,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>12.93066596984863</v>
+        <v>12.93066692352295</v>
       </c>
       <c r="C58" t="n">
         <v>17.84000015258789</v>
@@ -1659,7 +1659,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>13.08771514892578</v>
+        <v>13.08770942687988</v>
       </c>
       <c r="C59" t="n">
         <v>18.05666732788086</v>
@@ -1684,7 +1684,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>13.06838798522949</v>
+        <v>13.06838321685791</v>
       </c>
       <c r="C60" t="n">
         <v>18.03000068664551</v>
@@ -1709,7 +1709,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>13.1017894744873</v>
+        <v>13.10179233551025</v>
       </c>
       <c r="C61" t="n">
         <v>17.9766674041748</v>
@@ -1734,7 +1734,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>13.62168121337891</v>
+        <v>13.62168216705322</v>
       </c>
       <c r="C62" t="n">
         <v>18.69000053405762</v>
@@ -1759,7 +1759,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>12.62805461883545</v>
+        <v>12.62804889678955</v>
       </c>
       <c r="C63" t="n">
         <v>17.32666778564453</v>
@@ -1784,7 +1784,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>12.7336893081665</v>
+        <v>12.73368835449219</v>
       </c>
       <c r="C64" t="n">
         <v>17.35000038146973</v>
@@ -1813,7 +1813,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>13.45049571990967</v>
+        <v>13.45049095153809</v>
       </c>
       <c r="C65" t="n">
         <v>18.32666778564453</v>
@@ -1842,7 +1842,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>13.59859275817871</v>
+        <v>13.59859657287598</v>
       </c>
       <c r="C66" t="n">
         <v>18.40666770935059</v>
@@ -1871,7 +1871,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>13.08636856079102</v>
+        <v>13.08636474609375</v>
       </c>
       <c r="C67" t="n">
         <v>17.71333312988281</v>
@@ -1900,7 +1900,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>12.98047924041748</v>
+        <v>12.9804744720459</v>
       </c>
       <c r="C68" t="n">
         <v>17.56999969482422</v>
@@ -1929,7 +1929,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>13.19344043731689</v>
+        <v>13.19344329833984</v>
       </c>
       <c r="C69" t="n">
         <v>17.72999954223633</v>
@@ -1958,7 +1958,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>12.87346172332764</v>
+        <v>12.8734655380249</v>
       </c>
       <c r="C70" t="n">
         <v>17.29999923706055</v>
@@ -1987,7 +1987,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>14.06903839111328</v>
+        <v>14.06903553009033</v>
       </c>
       <c r="C71" t="n">
         <v>18.90666770935059</v>
@@ -2016,7 +2016,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>14.60976219177246</v>
+        <v>14.60977172851562</v>
       </c>
       <c r="C72" t="n">
         <v>19.63333320617676</v>
@@ -2045,7 +2045,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>14.91570377349854</v>
+        <v>14.91571140289307</v>
       </c>
       <c r="C73" t="n">
         <v>19.92000007629395</v>
@@ -2074,7 +2074,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>15.31505584716797</v>
+        <v>15.31505870819092</v>
       </c>
       <c r="C74" t="n">
         <v>20.45333290100098</v>
@@ -2103,7 +2103,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>14.74598121643066</v>
+        <v>14.74598693847656</v>
       </c>
       <c r="C75" t="n">
         <v>19.69333267211914</v>
@@ -2132,7 +2132,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>15.377366065979</v>
+        <v>15.37736225128174</v>
       </c>
       <c r="C76" t="n">
         <v>20.39999961853027</v>
@@ -2161,7 +2161,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>14.80196857452393</v>
+        <v>14.80196762084961</v>
       </c>
       <c r="C77" t="n">
         <v>19.63666725158691</v>
@@ -2190,7 +2190,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>16.65043640136719</v>
+        <v>16.65043067932129</v>
       </c>
       <c r="C78" t="n">
         <v>21.94000053405762</v>
@@ -2219,7 +2219,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>17.63701057434082</v>
+        <v>17.63701248168945</v>
       </c>
       <c r="C79" t="n">
         <v>23.23999977111816</v>
@@ -2248,7 +2248,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>18.8284912109375</v>
+        <v>18.82849502563477</v>
       </c>
       <c r="C80" t="n">
         <v>24.80999946594238</v>
@@ -2335,7 +2335,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>19.08037567138672</v>
+        <v>19.08037948608398</v>
       </c>
       <c r="C83" t="n">
         <v>25.00666618347168</v>
@@ -2364,7 +2364,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>18.3173656463623</v>
+        <v>18.3173713684082</v>
       </c>
       <c r="C84" t="n">
         <v>24.00666618347168</v>
@@ -2393,7 +2393,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>17.44972801208496</v>
+        <v>17.44972610473633</v>
       </c>
       <c r="C85" t="n">
         <v>22.74333381652832</v>
@@ -2422,7 +2422,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>17.88962364196777</v>
+        <v>17.88961601257324</v>
       </c>
       <c r="C86" t="n">
         <v>23.3166675567627</v>
@@ -2509,7 +2509,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>20.00502395629883</v>
+        <v>20.0050220489502</v>
       </c>
       <c r="C89" t="n">
         <v>25.90666770935059</v>
@@ -2538,7 +2538,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>19.3792552947998</v>
+        <v>19.37924766540527</v>
       </c>
       <c r="C90" t="n">
         <v>24.9466667175293</v>
@@ -2567,7 +2567,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>19.28862571716309</v>
+        <v>19.28861999511719</v>
       </c>
       <c r="C91" t="n">
         <v>24.82999992370605</v>
@@ -2596,7 +2596,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>20.18198204040527</v>
+        <v>20.18197059631348</v>
       </c>
       <c r="C92" t="n">
         <v>25.97999954223633</v>
@@ -2625,7 +2625,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>19.01237297058105</v>
+        <v>19.01237678527832</v>
       </c>
       <c r="C93" t="n">
         <v>24.32666778564453</v>
@@ -2654,7 +2654,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>19.26767730712891</v>
+        <v>19.2676830291748</v>
       </c>
       <c r="C94" t="n">
         <v>24.65333366394043</v>
@@ -2683,7 +2683,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>19.99452018737793</v>
+        <v>19.9945125579834</v>
       </c>
       <c r="C95" t="n">
         <v>25.58333206176758</v>
@@ -2712,7 +2712,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>21.10431289672852</v>
+        <v>21.10430335998535</v>
       </c>
       <c r="C96" t="n">
         <v>27.00333213806152</v>
@@ -2741,7 +2741,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>20.61924362182617</v>
+        <v>20.61924171447754</v>
       </c>
       <c r="C97" t="n">
         <v>26.22999954223633</v>
@@ -2770,7 +2770,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>19.56850242614746</v>
+        <v>19.56850433349609</v>
       </c>
       <c r="C98" t="n">
         <v>24.89333343505859</v>
@@ -2799,7 +2799,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>19.57374382019043</v>
+        <v>19.5737419128418</v>
       </c>
       <c r="C99" t="n">
         <v>24.89999961853027</v>
@@ -2857,7 +2857,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>21.02126502990723</v>
+        <v>21.02127075195312</v>
       </c>
       <c r="C101" t="n">
         <v>26.56999969482422</v>
@@ -2886,7 +2886,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>20.37126922607422</v>
+        <v>20.37127113342285</v>
       </c>
       <c r="C102" t="n">
         <v>25.59000015258789</v>
@@ -2944,7 +2944,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>19.52478981018066</v>
+        <v>19.52479362487793</v>
       </c>
       <c r="C104" t="n">
         <v>24.52666664123535</v>
@@ -2973,7 +2973,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>20.166259765625</v>
+        <v>20.1662654876709</v>
       </c>
       <c r="C105" t="n">
         <v>25.16666793823242</v>
@@ -3002,7 +3002,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>20.42535591125488</v>
+        <v>20.42535400390625</v>
       </c>
       <c r="C106" t="n">
         <v>25.48999977111816</v>
@@ -3031,7 +3031,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>20.37192916870117</v>
+        <v>20.37192726135254</v>
       </c>
       <c r="C107" t="n">
         <v>25.42333221435547</v>
@@ -3060,7 +3060,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>23.38217926025391</v>
+        <v>23.38218307495117</v>
       </c>
       <c r="C108" t="n">
         <v>29.18000030517578</v>
@@ -3089,7 +3089,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>23.06693649291992</v>
+        <v>23.06694030761719</v>
       </c>
       <c r="C109" t="n">
         <v>28.62666702270508</v>
@@ -3118,7 +3118,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>22.82520294189453</v>
+        <v>22.8252010345459</v>
       </c>
       <c r="C110" t="n">
         <v>28.32666778564453</v>
@@ -3147,7 +3147,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>22.54317283630371</v>
+        <v>22.54318237304688</v>
       </c>
       <c r="C111" t="n">
         <v>27.9766674041748</v>
@@ -3176,7 +3176,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>22.22462844848633</v>
+        <v>22.22463035583496</v>
       </c>
       <c r="C112" t="n">
         <v>27.41666793823242</v>
@@ -3205,7 +3205,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>21.08976364135742</v>
+        <v>21.08975601196289</v>
       </c>
       <c r="C113" t="n">
         <v>26.01666641235352</v>
@@ -3234,7 +3234,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>20.19502067565918</v>
+        <v>20.19502449035645</v>
       </c>
       <c r="C114" t="n">
         <v>24.75666618347168</v>
@@ -3263,7 +3263,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>19.28682708740234</v>
+        <v>19.28683090209961</v>
       </c>
       <c r="C115" t="n">
         <v>23.64333343505859</v>
@@ -3379,7 +3379,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>15.67061424255371</v>
+        <v>15.67061328887939</v>
       </c>
       <c r="C119" t="n">
         <v>19.07999992370605</v>
@@ -3408,7 +3408,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>16.10863876342773</v>
+        <v>16.1086483001709</v>
       </c>
       <c r="C120" t="n">
         <v>19.61333274841309</v>
@@ -3437,7 +3437,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>16.92268943786621</v>
+        <v>16.92269134521484</v>
       </c>
       <c r="C121" t="n">
         <v>20.4333324432373</v>
@@ -3466,7 +3466,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>18.31956672668457</v>
+        <v>18.31957054138184</v>
       </c>
       <c r="C122" t="n">
         <v>22.1200008392334</v>
@@ -3495,7 +3495,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>18.31404685974121</v>
+        <v>18.31404876708984</v>
       </c>
       <c r="C123" t="n">
         <v>22.11333274841309</v>
@@ -3524,7 +3524,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>19.04755973815918</v>
+        <v>19.04755592346191</v>
       </c>
       <c r="C124" t="n">
         <v>22.82999992370605</v>
@@ -3553,7 +3553,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>18.59702301025391</v>
+        <v>18.59702491760254</v>
       </c>
       <c r="C125" t="n">
         <v>22.29000091552734</v>
@@ -3582,7 +3582,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>19.82854652404785</v>
+        <v>19.82854270935059</v>
       </c>
       <c r="C126" t="n">
         <v>23.59333229064941</v>
@@ -3611,7 +3611,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>20.4560661315918</v>
+        <v>20.45606994628906</v>
       </c>
       <c r="C127" t="n">
         <v>24.34000015258789</v>
@@ -3640,7 +3640,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>20.44205856323242</v>
+        <v>20.44206428527832</v>
       </c>
       <c r="C128" t="n">
         <v>24.32333374023438</v>
@@ -3669,7 +3669,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>20.15044403076172</v>
+        <v>20.15044784545898</v>
       </c>
       <c r="C129" t="n">
         <v>23.81333351135254</v>
@@ -3698,7 +3698,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>20.34224319458008</v>
+        <v>20.34224700927734</v>
       </c>
       <c r="C130" t="n">
         <v>24.04000091552734</v>
@@ -3727,7 +3727,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>19.74991416931152</v>
+        <v>19.74991989135742</v>
       </c>
       <c r="C131" t="n">
         <v>23.34000015258789</v>
@@ -3756,7 +3756,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>19.86556434631348</v>
+        <v>19.86555862426758</v>
       </c>
       <c r="C132" t="n">
         <v>23.4766674041748</v>
@@ -3785,7 +3785,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>19.63559722900391</v>
+        <v>19.63560485839844</v>
       </c>
       <c r="C133" t="n">
         <v>23.04000091552734</v>
@@ -3814,7 +3814,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>18.9594898223877</v>
+        <v>18.95949554443359</v>
       </c>
       <c r="C134" t="n">
         <v>22.24666786193848</v>
@@ -3843,7 +3843,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>20.14978408813477</v>
+        <v>20.14978218078613</v>
       </c>
       <c r="C135" t="n">
         <v>23.64333343505859</v>
@@ -3872,7 +3872,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>20.62703323364258</v>
+        <v>20.62703514099121</v>
       </c>
       <c r="C136" t="n">
         <v>24.02666664123535</v>
@@ -3901,7 +3901,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>21.5141544342041</v>
+        <v>21.5141658782959</v>
       </c>
       <c r="C137" t="n">
         <v>25.05999946594238</v>
@@ -3930,7 +3930,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>22.64338111877441</v>
+        <v>22.64337921142578</v>
       </c>
       <c r="C138" t="n">
         <v>26.20000076293945</v>
@@ -3959,7 +3959,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>21.80217933654785</v>
+        <v>21.80217742919922</v>
       </c>
       <c r="C139" t="n">
         <v>25.2266674041748</v>
@@ -3988,7 +3988,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>23.04381942749023</v>
+        <v>23.04380798339844</v>
       </c>
       <c r="C140" t="n">
         <v>26.66333389282227</v>
@@ -4017,7 +4017,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>22.63216781616211</v>
+        <v>22.63216018676758</v>
       </c>
       <c r="C141" t="n">
         <v>26.0233325958252</v>
@@ -4046,7 +4046,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>22.65245246887207</v>
+        <v>22.6524600982666</v>
       </c>
       <c r="C142" t="n">
         <v>26.04666709899902</v>
@@ -4075,7 +4075,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>25.31080055236816</v>
+        <v>25.31079864501953</v>
       </c>
       <c r="C143" t="n">
         <v>29.10333251953125</v>
@@ -4104,7 +4104,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>28.18656921386719</v>
+        <v>28.18657112121582</v>
       </c>
       <c r="C144" t="n">
         <v>32.40999984741211</v>
@@ -4133,7 +4133,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>28.77808380126953</v>
+        <v>28.77807807922363</v>
       </c>
       <c r="C145" t="n">
         <v>32.91666793823242</v>
@@ -4162,7 +4162,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>31.06575775146484</v>
+        <v>31.06575393676758</v>
       </c>
       <c r="C146" t="n">
         <v>35.53333282470703</v>
@@ -4191,7 +4191,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>26.23103332519531</v>
+        <v>26.23103523254395</v>
       </c>
       <c r="C147" t="n">
         <v>30.00333213806152</v>
@@ -4278,7 +4278,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>24.34995269775391</v>
+        <v>24.34995460510254</v>
       </c>
       <c r="C150" t="n">
         <v>27.51333236694336</v>
@@ -4336,7 +4336,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>26.32355690002441</v>
+        <v>26.32355880737305</v>
       </c>
       <c r="C152" t="n">
         <v>29.74333381652832</v>
@@ -4365,7 +4365,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>28.44370651245117</v>
+        <v>28.4437084197998</v>
       </c>
       <c r="C153" t="n">
         <v>31.95333290100098</v>
@@ -4394,7 +4394,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>27.86509895324707</v>
+        <v>27.86510467529297</v>
       </c>
       <c r="C154" t="n">
         <v>31.3033332824707</v>
@@ -4423,7 +4423,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>29.75521659851074</v>
+        <v>29.75521469116211</v>
       </c>
       <c r="C155" t="n">
         <v>33.42666625976562</v>
@@ -4452,7 +4452,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>28.97484397888184</v>
+        <v>28.97483825683594</v>
       </c>
       <c r="C156" t="n">
         <v>32.54999923706055</v>
@@ -4481,7 +4481,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>27.79042434692383</v>
+        <v>27.79042816162109</v>
       </c>
       <c r="C157" t="n">
         <v>31.04999923706055</v>
@@ -4510,7 +4510,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>28.58997535705566</v>
+        <v>28.58997917175293</v>
       </c>
       <c r="C158" t="n">
         <v>31.94333267211914</v>
@@ -4539,7 +4539,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>29.53274345397949</v>
+        <v>29.53272819519043</v>
       </c>
       <c r="C159" t="n">
         <v>32.99666595458984</v>
@@ -4568,7 +4568,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>29.25372123718262</v>
+        <v>29.25371742248535</v>
       </c>
       <c r="C160" t="n">
         <v>32.5099983215332</v>
@@ -4597,7 +4597,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>30.8464298248291</v>
+        <v>30.84642791748047</v>
       </c>
       <c r="C161" t="n">
         <v>34.27999877929688</v>
@@ -4626,7 +4626,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>30.588134765625</v>
+        <v>30.5881404876709</v>
       </c>
       <c r="C162" t="n">
         <v>33.81333160400391</v>
@@ -4684,7 +4684,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>33.28389739990234</v>
+        <v>33.28390121459961</v>
       </c>
       <c r="C164" t="n">
         <v>36.79333114624023</v>
@@ -4713,7 +4713,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>34.62347412109375</v>
+        <v>34.62347793579102</v>
       </c>
       <c r="C165" t="n">
         <v>38.08666610717773</v>
@@ -4742,7 +4742,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>35.96284484863281</v>
+        <v>35.96285247802734</v>
       </c>
       <c r="C166" t="n">
         <v>39.56000137329102</v>
@@ -4771,7 +4771,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>35.53253936767578</v>
+        <v>35.53254699707031</v>
       </c>
       <c r="C167" t="n">
         <v>39.08666610717773</v>
@@ -4800,7 +4800,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>36.08707046508789</v>
+        <v>36.08707427978516</v>
       </c>
       <c r="C168" t="n">
         <v>39.6966667175293</v>
@@ -4829,7 +4829,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>36.17284774780273</v>
+        <v>36.17283630371094</v>
       </c>
       <c r="C169" t="n">
         <v>39.61333465576172</v>
@@ -4858,7 +4858,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>34.84877777099609</v>
+        <v>34.84878540039062</v>
       </c>
       <c r="C170" t="n">
         <v>38.16333389282227</v>
@@ -4887,7 +4887,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>32.77593612670898</v>
+        <v>32.77593994140625</v>
       </c>
       <c r="C171" t="n">
         <v>35.89333343505859</v>
@@ -4916,7 +4916,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>34.73698806762695</v>
+        <v>34.73698425292969</v>
       </c>
       <c r="C172" t="n">
         <v>37.87333297729492</v>
@@ -4945,7 +4945,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>37.16143035888672</v>
+        <v>37.16142654418945</v>
       </c>
       <c r="C173" t="n">
         <v>40.51666641235352</v>
@@ -4974,7 +4974,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>38.09564971923828</v>
+        <v>38.09565353393555</v>
       </c>
       <c r="C174" t="n">
         <v>41.35333251953125</v>
@@ -5003,7 +5003,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>36.78136825561523</v>
+        <v>36.78137588500977</v>
       </c>
       <c r="C175" t="n">
         <v>39.92666625976562</v>
@@ -5032,7 +5032,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>39.73543167114258</v>
+        <v>39.73542404174805</v>
       </c>
       <c r="C176" t="n">
         <v>43.13333129882812</v>
@@ -5061,7 +5061,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>42.81257629394531</v>
+        <v>42.81258010864258</v>
       </c>
       <c r="C177" t="n">
         <v>46.28333282470703</v>
@@ -5119,7 +5119,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>42.78174209594727</v>
+        <v>42.78174591064453</v>
       </c>
       <c r="C179" t="n">
         <v>46.25</v>
@@ -5148,7 +5148,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>47.11079025268555</v>
+        <v>47.11078643798828</v>
       </c>
       <c r="C180" t="n">
         <v>50.93000030517578</v>
@@ -5177,7 +5177,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>44.60922241210938</v>
+        <v>44.60923004150391</v>
       </c>
       <c r="C181" t="n">
         <v>48.04999923706055</v>
@@ -5206,7 +5206,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>43.47658920288086</v>
+        <v>43.47659301757812</v>
       </c>
       <c r="C182" t="n">
         <v>46.83000183105469</v>
@@ -5235,7 +5235,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>40.20555877685547</v>
+        <v>40.2055549621582</v>
       </c>
       <c r="C183" t="n">
         <v>43.30666732788086</v>
@@ -5322,7 +5322,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>44.31000137329102</v>
+        <v>44.31000900268555</v>
       </c>
       <c r="C186" t="n">
         <v>47.34333419799805</v>
@@ -5351,7 +5351,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>43.99491500854492</v>
+        <v>43.99490737915039</v>
       </c>
       <c r="C187" t="n">
         <v>47.00666809082031</v>
@@ -5380,7 +5380,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>44.47223281860352</v>
+        <v>44.47224044799805</v>
       </c>
       <c r="C188" t="n">
         <v>47.51666641235352</v>
@@ -5409,7 +5409,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>46.37373352050781</v>
+        <v>46.37373733520508</v>
       </c>
       <c r="C189" t="n">
         <v>49.36666870117188</v>
@@ -5467,7 +5467,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>46.78705215454102</v>
+        <v>46.78704833984375</v>
       </c>
       <c r="C191" t="n">
         <v>49.80666732788086</v>
@@ -5496,7 +5496,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>44.03469085693359</v>
+        <v>44.03468704223633</v>
       </c>
       <c r="C192" t="n">
         <v>46.87666702270508</v>
@@ -5525,7 +5525,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>45.4883918762207</v>
+        <v>45.48838424682617</v>
       </c>
       <c r="C193" t="n">
         <v>48.22999954223633</v>
@@ -5554,7 +5554,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>43.95419311523438</v>
+        <v>43.95418930053711</v>
       </c>
       <c r="C194" t="n">
         <v>46.60333251953125</v>
@@ -5583,7 +5583,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>42.49230194091797</v>
+        <v>42.49230575561523</v>
       </c>
       <c r="C195" t="n">
         <v>45.0533332824707</v>
@@ -5699,7 +5699,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>38.51026153564453</v>
+        <v>38.51025772094727</v>
       </c>
       <c r="C199" t="n">
         <v>40.52666854858398</v>
@@ -5728,7 +5728,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>41.82660675048828</v>
+        <v>41.82661437988281</v>
       </c>
       <c r="C200" t="n">
         <v>44.01666641235352</v>
@@ -5757,7 +5757,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>42.16785430908203</v>
+        <v>42.16784286499023</v>
       </c>
       <c r="C201" t="n">
         <v>44.18333435058594</v>
@@ -5786,7 +5786,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>41.26118850708008</v>
+        <v>41.26117706298828</v>
       </c>
       <c r="C202" t="n">
         <v>43.23333358764648</v>
@@ -5844,7 +5844,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>48.48904037475586</v>
+        <v>48.48904800415039</v>
       </c>
       <c r="C204" t="n">
         <v>50.80666732788086</v>
@@ -5873,7 +5873,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>45.27739715576172</v>
+        <v>45.27738952636719</v>
       </c>
       <c r="C205" t="n">
         <v>47.26333236694336</v>
@@ -5931,7 +5931,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>45.38596725463867</v>
+        <v>45.38596343994141</v>
       </c>
       <c r="C207" t="n">
         <v>47.37666702270508</v>
@@ -5960,7 +5960,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>47.27776336669922</v>
+        <v>47.27776718139648</v>
       </c>
       <c r="C208" t="n">
         <v>49.15000152587891</v>
@@ -5989,7 +5989,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>48.40640258789062</v>
+        <v>48.40640640258789</v>
       </c>
       <c r="C209" t="n">
         <v>50.32333374023438</v>
@@ -6047,7 +6047,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>50.58899307250977</v>
+        <v>50.5890007019043</v>
       </c>
       <c r="C211" t="n">
         <v>52.39333343505859</v>
@@ -6076,7 +6076,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>51.45157241821289</v>
+        <v>51.45156860351562</v>
       </c>
       <c r="C212" t="n">
         <v>53.28666687011719</v>
@@ -6105,7 +6105,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>52.52272415161133</v>
+        <v>52.52272796630859</v>
       </c>
       <c r="C213" t="n">
         <v>54.20333480834961</v>
@@ -6134,7 +6134,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>51.65708541870117</v>
+        <v>51.6570930480957</v>
       </c>
       <c r="C214" t="n">
         <v>53.31000137329102</v>
@@ -6163,7 +6163,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>52.78112030029297</v>
+        <v>52.78111267089844</v>
       </c>
       <c r="C215" t="n">
         <v>54.47000122070312</v>
@@ -6192,7 +6192,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>50.28757476806641</v>
+        <v>50.28757095336914</v>
       </c>
       <c r="C216" t="n">
         <v>51.89666748046875</v>
@@ -6221,7 +6221,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>51.10976791381836</v>
+        <v>51.10977554321289</v>
       </c>
       <c r="C217" t="n">
         <v>52.54999923706055</v>
@@ -6250,7 +6250,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>53.57367706298828</v>
+        <v>53.57368087768555</v>
       </c>
       <c r="C218" t="n">
         <v>55.08333206176758</v>
@@ -6279,7 +6279,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>57.00368881225586</v>
+        <v>57.00368499755859</v>
       </c>
       <c r="C219" t="n">
         <v>58.61000061035156</v>
@@ -6337,7 +6337,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>57.92000579833984</v>
+        <v>57.92000198364258</v>
       </c>
       <c r="C221" t="n">
         <v>59.34999847412109</v>
@@ -6366,7 +6366,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>64.397705078125</v>
+        <v>64.39768981933594</v>
       </c>
       <c r="C222" t="n">
         <v>65.76000213623047</v>
@@ -6395,7 +6395,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>66.30728912353516</v>
+        <v>66.30730438232422</v>
       </c>
       <c r="C223" t="n">
         <v>67.70999908447266</v>
@@ -6424,7 +6424,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>67.21804046630859</v>
+        <v>67.21803283691406</v>
       </c>
       <c r="C224" t="n">
         <v>68.63999938964844</v>
@@ -6453,7 +6453,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>75.84566497802734</v>
+        <v>75.84565734863281</v>
       </c>
       <c r="C225" t="n">
         <v>77.23000335693359</v>
@@ -6540,7 +6540,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>90.84193420410156</v>
+        <v>90.84194183349609</v>
       </c>
       <c r="C228" t="n">
         <v>92.5</v>
@@ -6569,7 +6569,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>88.92707824707031</v>
+        <v>88.92707061767578</v>
       </c>
       <c r="C229" t="n">
         <v>90.34999847412109</v>
@@ -6598,7 +6598,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>96.61406707763672</v>
+        <v>96.61408233642578</v>
       </c>
       <c r="C230" t="n">
         <v>98.16000366210938</v>
@@ -6656,7 +6656,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>86.64467620849609</v>
+        <v>86.64468383789062</v>
       </c>
       <c r="C232" t="n">
         <v>87.79000091552734</v>
@@ -6685,7 +6685,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>95.98125457763672</v>
+        <v>95.98124694824219</v>
       </c>
       <c r="C233" t="n">
         <v>97.25</v>
@@ -6714,7 +6714,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>97.66765594482422</v>
+        <v>97.66764831542969</v>
       </c>
       <c r="C234" t="n">
         <v>98.72000122070312</v>
@@ -6743,7 +6743,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>96.73766326904297</v>
+        <v>96.7376708984375</v>
       </c>
       <c r="C235" t="n">
         <v>97.77999877929688</v>
@@ -6772,7 +6772,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>96.93553924560547</v>
+        <v>96.935546875</v>
       </c>
       <c r="C236" t="n">
         <v>97.98000335693359</v>
@@ -6801,7 +6801,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>96.1702880859375</v>
+        <v>96.17029571533203</v>
       </c>
       <c r="C237" t="n">
         <v>96.98000335693359</v>
@@ -6859,7 +6859,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>100.3352279663086</v>
+        <v>100.3352127075195</v>
       </c>
       <c r="C239" t="n">
         <v>101.1800003051758</v>
@@ -6946,7 +6946,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>118.386100769043</v>
+        <v>118.3861083984375</v>
       </c>
       <c r="C242" t="n">
         <v>119.1399993896484</v>
